--- a/data/trans_dic/IP31KM08_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM08_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 6,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,66</t>
+          <t>0,37; 4,17</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,53; 39,33</t>
+          <t>27,09; 45,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,66; 44,53</t>
+          <t>27,18; 43,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,35; 38,08</t>
+          <t>29,29; 41,46</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,0; 57,9</t>
+          <t>35,54; 54,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,51; 55,22</t>
+          <t>37,27; 56,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,85; 53,77</t>
+          <t>38,51; 53,59</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,08; 57,48</t>
+          <t>22,94; 52,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,27; 50,77</t>
+          <t>34,23; 55,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,97; 49,28</t>
+          <t>31,42; 51,1</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,47; 45,96</t>
+          <t>29,12; 52,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,56; 54,16</t>
+          <t>22,79; 46,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,02; 46,31</t>
+          <t>28,71; 45,6</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,46; 43,14</t>
+          <t>18,02; 38,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,59; 38,0</t>
+          <t>21,7; 43,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,35; 36,77</t>
+          <t>22,96; 37,5</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,99; 59,56</t>
+          <t>46,1; 62,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,35; 64,89</t>
+          <t>41,81; 57,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,39; 60,33</t>
+          <t>46,75; 57,64</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,03; 81,95</t>
+          <t>66,57; 79,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>66,78; 79,41</t>
+          <t>70,15; 82,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69,19; 78,78</t>
+          <t>70,98; 79,76</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36,82; 46,72</t>
+          <t>42,18; 49,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41,04; 48,56</t>
+          <t>42,87; 49,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,79; 46,73</t>
+          <t>43,31; 48,52</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>886</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>705</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1592</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3937</t>
+          <t>0; 3124</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3754</t>
+          <t>0; 3515</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>485; 5338</t>
+          <t>431; 4808</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>35228</t>
+          <t>40750</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79764</t>
+          <t>76025</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15746; 49415</t>
+          <t>31142; 52057</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33701; 56296</t>
+          <t>26997; 42785</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53807; 95980</t>
+          <t>62760; 88851</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>25788</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29078</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55333</t>
+          <t>51082</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19997; 32163</t>
+          <t>20363; 31294</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22303; 35693</t>
+          <t>20167; 30559</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46692; 64622</t>
+          <t>42903; 59708</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31737</t>
+          <t>25956</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26904</t>
+          <t>31699</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58642</t>
+          <t>57655</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25144; 40051</t>
+          <t>16018; 36302</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15277; 38263</t>
+          <t>24122; 39088</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43472; 71481</t>
+          <t>44074; 71682</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>27547</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7343; 15720</t>
+          <t>11524; 20580</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12038; 22052</t>
+          <t>8060; 16480</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21742; 34694</t>
+          <t>21522; 34178</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28773</t>
+          <t>27137</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9946; 19109</t>
+          <t>8505; 18217</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9998; 20440</t>
+          <t>9609; 19109</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21922; 36065</t>
+          <t>21006; 34311</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>64611</t>
+          <t>77070</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>87404</t>
+          <t>61091</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152015</t>
+          <t>138162</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>54417; 73676</t>
+          <t>64801; 87258</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>73418; 100602</t>
+          <t>50939; 70502</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>134887; 168171</t>
+          <t>122672; 151234</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>136</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>97933</t>
+          <t>115181</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>113169</t>
+          <t>106841</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>211101</t>
+          <t>222022</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>90107; 105443</t>
+          <t>104605; 125219</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>102953; 122423</t>
+          <t>96733; 114387</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>195683; 222811</t>
+          <t>209419; 235314</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>406</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>282089</t>
+          <t>314265</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>286956</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>615865</t>
+          <t>601221</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>240513; 305116</t>
+          <t>289722; 339438</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>305651; 361634</t>
+          <t>265036; 307614</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>570122; 653213</t>
+          <t>565196; 633148</t>
         </is>
       </c>
     </row>
